--- a/backend/data/ST1131_Quiz2.xlsx
+++ b/backend/data/ST1131_Quiz2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/extracted_questions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhixin/Documents/y4s1/dsa3101/dsa3101-2510-quiz-02/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CB499BC-CFB9-D442-B8B5-4B6AFC4889BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBDA930-0648-3547-8C6A-3F0078F39872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14760" yWindow="920" windowWidth="14480" windowHeight="16420" activeTab="1" xr2:uid="{CA20E2D9-AC26-2B4B-A400-E03C0BFEE2BC}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{CA20E2D9-AC26-2B4B-A400-E03C0BFEE2BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Context" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
   <si>
-    <t>Context ID</t>
-  </si>
-  <si>
     <t>Context Text</t>
   </si>
   <si>
@@ -238,6 +235,9 @@
   </si>
   <si>
     <t>EDA, Basic Concepts in Statistics, Boxplot</t>
+  </si>
+  <si>
+    <t>Context ID</t>
   </si>
 </sst>
 </file>
@@ -617,13 +617,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -646,52 +646,52 @@
   <sheetData>
     <row r="1" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
-        <v>12</v>
-      </c>
       <c r="P1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="102" x14ac:dyDescent="0.2">
@@ -699,25 +699,25 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="M2">
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="136" x14ac:dyDescent="0.2">
@@ -725,28 +725,28 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>24</v>
       </c>
-      <c r="G3" t="s">
+      <c r="K3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="M3">
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="51" x14ac:dyDescent="0.2">
@@ -754,34 +754,34 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M4">
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="136" x14ac:dyDescent="0.2">
@@ -789,25 +789,25 @@
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="M5">
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="102" x14ac:dyDescent="0.2">
@@ -815,31 +815,31 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6" t="s">
+        <v>50</v>
+      </c>
+      <c r="O6" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" t="s">
         <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6" t="s">
-        <v>51</v>
-      </c>
-      <c r="O6" t="s">
-        <v>55</v>
-      </c>
-      <c r="P6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -847,10 +847,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -859,16 +859,16 @@
         <v>0</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="34" x14ac:dyDescent="0.2">
@@ -876,10 +876,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -888,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="119" x14ac:dyDescent="0.2">
@@ -905,31 +905,31 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="153" x14ac:dyDescent="0.2">
@@ -937,34 +937,34 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
         <v>48</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" t="s">
-        <v>46</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10" t="s">
         <v>50</v>
       </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="O10" t="s">
         <v>51</v>
       </c>
-      <c r="O10" t="s">
-        <v>52</v>
-      </c>
       <c r="P10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
